--- a/packages/calculators/src/modules/test/16-lulucf/16.2-lulucf.xlsx
+++ b/packages/calculators/src/modules/test/16-lulucf/16.2-lulucf.xlsx
@@ -1,14 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/16-lulucf/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2D38DC-5093-8343-98D9-A5C4A993970F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E367995-F5BA-F545-87C6-565B5D43AB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{CC0FEAF9-C40F-694B-BCB9-117AFB86C05D}"/>
   </bookViews>
@@ -18,6 +13,9 @@
     <sheet name="16.2.1.5" sheetId="3" r:id="rId3"/>
     <sheet name="16.2.1.7" sheetId="4" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -633,6 +631,31 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cco2" refersTo="='common'!$B$2"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="B2">
+            <v>3.67</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1004,8 +1027,8 @@
         <v>23</v>
       </c>
       <c r="P7">
-        <f>44/12</f>
-        <v>3.6666666666666665</v>
+        <f>[1]!common_cco2</f>
+        <v>3.67</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
@@ -1128,11 +1151,11 @@
       </c>
       <c r="J11">
         <f>$P$7</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="K11">
         <f>I11*J11*-1</f>
-        <v>-183.33333333333331</v>
+        <v>-183.5</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
@@ -1168,11 +1191,11 @@
       </c>
       <c r="J12">
         <f>$P$7</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="K12">
         <f>I12*J12*-1</f>
-        <v>7150</v>
+        <v>7156.5</v>
       </c>
     </row>
   </sheetData>
@@ -1363,8 +1386,8 @@
         <v>23</v>
       </c>
       <c r="M7">
-        <f>44/12</f>
-        <v>3.6666666666666665</v>
+        <f>[1]!common_cco2</f>
+        <v>3.67</v>
       </c>
     </row>
     <row r="9" spans="1:13" s="1" customFormat="1" ht="51" x14ac:dyDescent="0.2">
@@ -1418,11 +1441,11 @@
       </c>
       <c r="E11">
         <f>$M$7</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F11">
         <f>D11*E11*-1</f>
-        <v>0.43999999999999995</v>
+        <v>0.44039999999999996</v>
       </c>
       <c r="K11" t="s">
         <v>47</v>
@@ -1448,11 +1471,11 @@
       </c>
       <c r="E12">
         <f t="shared" ref="E12:E75" si="2">$M$7</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F12">
         <f t="shared" ref="F12:F75" si="3">D12*E12*-1</f>
-        <v>3.1533333333333333</v>
+        <v>3.1561999999999997</v>
       </c>
       <c r="K12" t="s">
         <v>48</v>
@@ -1478,11 +1501,11 @@
       </c>
       <c r="E13">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F13">
         <f t="shared" si="3"/>
-        <v>0.99</v>
+        <v>0.9909</v>
       </c>
       <c r="K13" t="s">
         <v>49</v>
@@ -1508,11 +1531,11 @@
       </c>
       <c r="E14">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F14">
         <f t="shared" si="3"/>
-        <v>1.3199999999999998</v>
+        <v>1.3211999999999999</v>
       </c>
       <c r="K14" t="s">
         <v>50</v>
@@ -1538,11 +1561,11 @@
       </c>
       <c r="E15">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F15">
         <f t="shared" si="3"/>
-        <v>2.5666666666666669</v>
+        <v>2.5690000000000004</v>
       </c>
       <c r="K15" t="s">
         <v>51</v>
@@ -1568,11 +1591,11 @@
       </c>
       <c r="E16">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F16">
         <f t="shared" si="3"/>
-        <v>2.86</v>
+        <v>2.8626</v>
       </c>
       <c r="K16" t="s">
         <v>52</v>
@@ -1598,11 +1621,11 @@
       </c>
       <c r="E17">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F17">
         <f t="shared" si="3"/>
-        <v>7.9566666666666661</v>
+        <v>7.9638999999999998</v>
       </c>
       <c r="K17" t="s">
         <v>53</v>
@@ -1628,11 +1651,11 @@
       </c>
       <c r="E18">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F18">
         <f t="shared" si="3"/>
-        <v>0.29333333333333333</v>
+        <v>0.29360000000000003</v>
       </c>
       <c r="K18" t="s">
         <v>54</v>
@@ -1658,11 +1681,11 @@
       </c>
       <c r="E19">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F19">
         <f t="shared" si="3"/>
-        <v>2.3100000000000005</v>
+        <v>2.3121000000000005</v>
       </c>
       <c r="K19" t="s">
         <v>55</v>
@@ -1688,11 +1711,11 @@
       </c>
       <c r="E20">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F20">
         <f t="shared" si="3"/>
-        <v>2.1999999999999997</v>
+        <v>2.202</v>
       </c>
       <c r="K20" t="s">
         <v>56</v>
@@ -1718,11 +1741,11 @@
       </c>
       <c r="E21">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F21">
         <f t="shared" si="3"/>
-        <v>3.63</v>
+        <v>3.6332999999999998</v>
       </c>
       <c r="K21" t="s">
         <v>57</v>
@@ -1748,11 +1771,11 @@
       </c>
       <c r="E22">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F22">
         <f t="shared" si="3"/>
-        <v>8.3600000000000012</v>
+        <v>8.3676000000000013</v>
       </c>
       <c r="K22" t="s">
         <v>58</v>
@@ -1778,11 +1801,11 @@
       </c>
       <c r="E23">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F23">
         <f t="shared" si="3"/>
-        <v>6.1966666666666663</v>
+        <v>6.2022999999999993</v>
       </c>
       <c r="K23" t="s">
         <v>59</v>
@@ -1808,11 +1831,11 @@
       </c>
       <c r="E24">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F24">
         <f t="shared" si="3"/>
-        <v>2.0533333333333332</v>
+        <v>2.0552000000000001</v>
       </c>
       <c r="K24" t="s">
         <v>60</v>
@@ -1838,11 +1861,11 @@
       </c>
       <c r="E25">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F25">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>22.02</v>
       </c>
       <c r="K25" t="s">
         <v>61</v>
@@ -1868,11 +1891,11 @@
       </c>
       <c r="E26">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F26">
         <f t="shared" si="3"/>
-        <v>5.2799999999999994</v>
+        <v>5.2847999999999997</v>
       </c>
       <c r="K26" t="s">
         <v>62</v>
@@ -1898,11 +1921,11 @@
       </c>
       <c r="E27">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F27">
         <f t="shared" si="3"/>
-        <v>2.4933333333333336</v>
+        <v>2.4956</v>
       </c>
       <c r="K27" t="s">
         <v>63</v>
@@ -1928,11 +1951,11 @@
       </c>
       <c r="E28">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F28">
         <f t="shared" si="3"/>
-        <v>29.04</v>
+        <v>29.066399999999998</v>
       </c>
       <c r="K28" t="s">
         <v>64</v>
@@ -1958,11 +1981,11 @@
       </c>
       <c r="E29">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F29">
         <f t="shared" si="3"/>
-        <v>14.629999999999999</v>
+        <v>14.643299999999998</v>
       </c>
       <c r="K29" t="s">
         <v>65</v>
@@ -1988,11 +2011,11 @@
       </c>
       <c r="E30">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F30">
         <f t="shared" si="3"/>
-        <v>15.4</v>
+        <v>15.414</v>
       </c>
       <c r="K30" t="s">
         <v>66</v>
@@ -2018,11 +2041,11 @@
       </c>
       <c r="E31">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F31">
         <f t="shared" si="3"/>
-        <v>14.63</v>
+        <v>14.6433</v>
       </c>
       <c r="K31" t="s">
         <v>67</v>
@@ -2048,11 +2071,11 @@
       </c>
       <c r="E32">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F32">
         <f t="shared" si="3"/>
-        <v>3.2266666666666666</v>
+        <v>3.2296</v>
       </c>
       <c r="K32" t="s">
         <v>68</v>
@@ -2078,11 +2101,11 @@
       </c>
       <c r="E33">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F33">
         <f t="shared" si="3"/>
-        <v>5.9033333333333333</v>
+        <v>5.9087000000000005</v>
       </c>
       <c r="K33" t="s">
         <v>69</v>
@@ -2108,11 +2131,11 @@
       </c>
       <c r="E34">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F34">
         <f t="shared" si="3"/>
-        <v>3.5199999999999996</v>
+        <v>3.5231999999999997</v>
       </c>
       <c r="K34" t="s">
         <v>70</v>
@@ -2138,11 +2161,11 @@
       </c>
       <c r="E35">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F35">
         <f t="shared" si="3"/>
-        <v>22.916666666666664</v>
+        <v>22.9375</v>
       </c>
       <c r="K35" t="s">
         <v>71</v>
@@ -2168,11 +2191,11 @@
       </c>
       <c r="E36">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F36">
         <f t="shared" si="3"/>
-        <v>16.206666666666667</v>
+        <v>16.221399999999999</v>
       </c>
       <c r="K36" t="s">
         <v>72</v>
@@ -2198,11 +2221,11 @@
       </c>
       <c r="E37">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F37">
         <f t="shared" si="3"/>
-        <v>2.9699999999999998</v>
+        <v>2.9726999999999997</v>
       </c>
       <c r="K37" t="s">
         <v>73</v>
@@ -2228,11 +2251,11 @@
       </c>
       <c r="E38">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F38">
         <f t="shared" si="3"/>
-        <v>2.0533333333333332</v>
+        <v>2.0552000000000001</v>
       </c>
       <c r="K38" t="s">
         <v>140</v>
@@ -2258,11 +2281,11 @@
       </c>
       <c r="E39">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F39">
         <f t="shared" si="3"/>
-        <v>45.723333333333336</v>
+        <v>45.764900000000004</v>
       </c>
       <c r="K39" t="s">
         <v>74</v>
@@ -2288,11 +2311,11 @@
       </c>
       <c r="E40">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F40">
         <f t="shared" si="3"/>
-        <v>15.4</v>
+        <v>15.414</v>
       </c>
       <c r="K40" t="s">
         <v>75</v>
@@ -2318,11 +2341,11 @@
       </c>
       <c r="E41">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F41">
         <f t="shared" si="3"/>
-        <v>3.4099999999999997</v>
+        <v>3.4130999999999996</v>
       </c>
       <c r="K41" t="s">
         <v>76</v>
@@ -2348,11 +2371,11 @@
       </c>
       <c r="E42">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F42">
         <f t="shared" si="3"/>
-        <v>14.079999999999998</v>
+        <v>14.092799999999999</v>
       </c>
       <c r="K42" t="s">
         <v>77</v>
@@ -2378,11 +2401,11 @@
       </c>
       <c r="E43">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F43">
         <f t="shared" si="3"/>
-        <v>15.729999999999999</v>
+        <v>15.744299999999999</v>
       </c>
       <c r="K43" t="s">
         <v>78</v>
@@ -2408,11 +2431,11 @@
       </c>
       <c r="E44">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F44">
         <f t="shared" si="3"/>
-        <v>19.946666666666669</v>
+        <v>19.9648</v>
       </c>
       <c r="K44" t="s">
         <v>79</v>
@@ -2438,11 +2461,11 @@
       </c>
       <c r="E45">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F45">
         <f t="shared" si="3"/>
-        <v>11.549999999999999</v>
+        <v>11.560499999999999</v>
       </c>
       <c r="K45" t="s">
         <v>80</v>
@@ -2468,11 +2491,11 @@
       </c>
       <c r="E46">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F46">
         <f t="shared" si="3"/>
-        <v>11.879999999999999</v>
+        <v>11.890799999999999</v>
       </c>
       <c r="K46" t="s">
         <v>81</v>
@@ -2498,11 +2521,11 @@
       </c>
       <c r="E47">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F47">
         <f t="shared" si="3"/>
-        <v>5.4266666666666667</v>
+        <v>5.4315999999999995</v>
       </c>
       <c r="K47" t="s">
         <v>82</v>
@@ -2528,11 +2551,11 @@
       </c>
       <c r="E48">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F48">
         <f t="shared" si="3"/>
-        <v>4.18</v>
+        <v>4.1837999999999997</v>
       </c>
       <c r="K48" t="s">
         <v>83</v>
@@ -2558,11 +2581,11 @@
       </c>
       <c r="E49">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F49">
         <f t="shared" si="3"/>
-        <v>20.020000000000003</v>
+        <v>20.038200000000003</v>
       </c>
       <c r="K49" t="s">
         <v>84</v>
@@ -2588,11 +2611,11 @@
       </c>
       <c r="E50">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F50">
         <f t="shared" si="3"/>
-        <v>45.466666666666669</v>
+        <v>45.508000000000003</v>
       </c>
       <c r="K50" t="s">
         <v>85</v>
@@ -2618,11 +2641,11 @@
       </c>
       <c r="E51">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F51">
         <f t="shared" si="3"/>
-        <v>34.576666666666661</v>
+        <v>34.6081</v>
       </c>
       <c r="K51" t="s">
         <v>86</v>
@@ -2648,11 +2671,11 @@
       </c>
       <c r="E52">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F52">
         <f t="shared" si="3"/>
-        <v>26.18</v>
+        <v>26.203800000000001</v>
       </c>
       <c r="K52" t="s">
         <v>87</v>
@@ -2678,11 +2701,11 @@
       </c>
       <c r="E53">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F53">
         <f t="shared" si="3"/>
-        <v>17.343333333333334</v>
+        <v>17.359100000000002</v>
       </c>
       <c r="K53" t="s">
         <v>88</v>
@@ -2708,11 +2731,11 @@
       </c>
       <c r="E54">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F54">
         <f t="shared" si="3"/>
-        <v>9.6799999999999979</v>
+        <v>9.6887999999999987</v>
       </c>
       <c r="K54" t="s">
         <v>89</v>
@@ -2738,11 +2761,11 @@
       </c>
       <c r="E55">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F55">
         <f t="shared" si="3"/>
-        <v>18.149999999999999</v>
+        <v>18.166499999999999</v>
       </c>
       <c r="K55" t="s">
         <v>90</v>
@@ -2768,11 +2791,11 @@
       </c>
       <c r="E56">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F56">
         <f t="shared" si="3"/>
-        <v>13.493333333333334</v>
+        <v>13.505600000000001</v>
       </c>
       <c r="K56" t="s">
         <v>91</v>
@@ -2798,11 +2821,11 @@
       </c>
       <c r="E57">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F57">
         <f t="shared" si="3"/>
-        <v>3.4466666666666668</v>
+        <v>3.4498000000000002</v>
       </c>
       <c r="K57" t="s">
         <v>92</v>
@@ -2828,11 +2851,11 @@
       </c>
       <c r="E58">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F58">
         <f t="shared" si="3"/>
-        <v>14.079999999999998</v>
+        <v>14.092799999999999</v>
       </c>
       <c r="K58" t="s">
         <v>93</v>
@@ -2858,11 +2881,11 @@
       </c>
       <c r="E59">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F59">
         <f t="shared" si="3"/>
-        <v>10.78</v>
+        <v>10.7898</v>
       </c>
       <c r="K59" t="s">
         <v>94</v>
@@ -2888,11 +2911,11 @@
       </c>
       <c r="E60">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F60">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>22.02</v>
       </c>
       <c r="K60" t="s">
         <v>95</v>
@@ -2918,11 +2941,11 @@
       </c>
       <c r="E61">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F61">
         <f t="shared" si="3"/>
-        <v>13.09</v>
+        <v>13.101900000000001</v>
       </c>
       <c r="K61" t="s">
         <v>96</v>
@@ -2948,11 +2971,11 @@
       </c>
       <c r="E62">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F62">
         <f t="shared" si="3"/>
-        <v>24.786666666666665</v>
+        <v>24.809199999999997</v>
       </c>
       <c r="K62" t="s">
         <v>97</v>
@@ -2978,11 +3001,11 @@
       </c>
       <c r="E63">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F63">
         <f t="shared" si="3"/>
-        <v>29.149999999999995</v>
+        <v>29.176499999999997</v>
       </c>
       <c r="K63" t="s">
         <v>98</v>
@@ -3008,11 +3031,11 @@
       </c>
       <c r="E64">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F64">
         <f t="shared" si="3"/>
-        <v>47.519999999999996</v>
+        <v>47.563199999999995</v>
       </c>
       <c r="K64" t="s">
         <v>99</v>
@@ -3038,11 +3061,11 @@
       </c>
       <c r="E65">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F65">
         <f t="shared" si="3"/>
-        <v>64.533333333333331</v>
+        <v>64.591999999999999</v>
       </c>
       <c r="K65" t="s">
         <v>100</v>
@@ -3068,11 +3091,11 @@
       </c>
       <c r="E66">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F66">
         <f t="shared" si="3"/>
-        <v>16.426666666666666</v>
+        <v>16.441600000000001</v>
       </c>
       <c r="K66" t="s">
         <v>101</v>
@@ -3098,7 +3121,7 @@
       </c>
       <c r="E67">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F67">
         <f t="shared" si="3"/>
@@ -3128,11 +3151,11 @@
       </c>
       <c r="E68">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F68">
         <f t="shared" si="3"/>
-        <v>34.026666666666664</v>
+        <v>34.057599999999994</v>
       </c>
       <c r="K68" t="s">
         <v>103</v>
@@ -3158,11 +3181,11 @@
       </c>
       <c r="E69">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F69">
         <f t="shared" si="3"/>
-        <v>71.39</v>
+        <v>71.454900000000009</v>
       </c>
       <c r="K69" t="s">
         <v>104</v>
@@ -3188,11 +3211,11 @@
       </c>
       <c r="E70">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F70">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>22.02</v>
       </c>
       <c r="K70" t="s">
         <v>105</v>
@@ -3218,11 +3241,11 @@
       </c>
       <c r="E71">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F71">
         <f t="shared" si="3"/>
-        <v>11.183333333333334</v>
+        <v>11.1935</v>
       </c>
       <c r="K71" t="s">
         <v>106</v>
@@ -3248,11 +3271,11 @@
       </c>
       <c r="E72">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F72">
         <f t="shared" si="3"/>
-        <v>59.106666666666669</v>
+        <v>59.160400000000003</v>
       </c>
       <c r="K72" t="s">
         <v>107</v>
@@ -3278,11 +3301,11 @@
       </c>
       <c r="E73">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F73">
         <f t="shared" si="3"/>
-        <v>60.059999999999995</v>
+        <v>60.114599999999996</v>
       </c>
       <c r="K73" t="s">
         <v>108</v>
@@ -3308,11 +3331,11 @@
       </c>
       <c r="E74">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F74">
         <f t="shared" si="3"/>
-        <v>7.0399999999999991</v>
+        <v>7.0463999999999993</v>
       </c>
       <c r="K74" t="s">
         <v>109</v>
@@ -3338,11 +3361,11 @@
       </c>
       <c r="E75">
         <f t="shared" si="2"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F75">
         <f t="shared" si="3"/>
-        <v>88.183333333333337</v>
+        <v>88.263500000000008</v>
       </c>
       <c r="K75" t="s">
         <v>110</v>
@@ -3368,11 +3391,11 @@
       </c>
       <c r="E76">
         <f t="shared" ref="E76:E94" si="6">$M$7</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F76">
         <f t="shared" ref="F76:F94" si="7">D76*E76*-1</f>
-        <v>7.26</v>
+        <v>7.2665999999999995</v>
       </c>
       <c r="K76" t="s">
         <v>111</v>
@@ -3398,11 +3421,11 @@
       </c>
       <c r="E77">
         <f t="shared" si="6"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F77">
         <f t="shared" si="7"/>
-        <v>7.3699999999999992</v>
+        <v>7.3766999999999987</v>
       </c>
       <c r="K77" t="s">
         <v>112</v>
@@ -3428,11 +3451,11 @@
       </c>
       <c r="E78">
         <f t="shared" si="6"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F78">
         <f t="shared" si="7"/>
-        <v>24.933333333333334</v>
+        <v>24.956000000000003</v>
       </c>
       <c r="K78" t="s">
         <v>113</v>
@@ -3458,11 +3481,11 @@
       </c>
       <c r="E79">
         <f t="shared" si="6"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F79">
         <f t="shared" si="7"/>
-        <v>63.25</v>
+        <v>63.307499999999997</v>
       </c>
       <c r="K79" t="s">
         <v>114</v>
@@ -3488,11 +3511,11 @@
       </c>
       <c r="E80">
         <f t="shared" si="6"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F80">
         <f t="shared" si="7"/>
-        <v>69.300000000000011</v>
+        <v>69.363</v>
       </c>
       <c r="K80" t="s">
         <v>115</v>
@@ -3518,11 +3541,11 @@
       </c>
       <c r="E81">
         <f t="shared" si="6"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F81">
         <f t="shared" si="7"/>
-        <v>46.859999999999992</v>
+        <v>46.9026</v>
       </c>
       <c r="K81" t="s">
         <v>116</v>
@@ -3548,11 +3571,11 @@
       </c>
       <c r="E82">
         <f t="shared" si="6"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F82">
         <f t="shared" si="7"/>
-        <v>31.68</v>
+        <v>31.7088</v>
       </c>
       <c r="K82" t="s">
         <v>117</v>
@@ -3578,11 +3601,11 @@
       </c>
       <c r="E83">
         <f t="shared" si="6"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F83">
         <f t="shared" si="7"/>
-        <v>85.653333333333322</v>
+        <v>85.731200000000001</v>
       </c>
       <c r="K83" t="s">
         <v>118</v>
@@ -3608,11 +3631,11 @@
       </c>
       <c r="E84">
         <f t="shared" si="6"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F84">
         <f t="shared" si="7"/>
-        <v>54.266666666666666</v>
+        <v>54.316000000000003</v>
       </c>
       <c r="K84" t="s">
         <v>119</v>
@@ -3638,11 +3661,11 @@
       </c>
       <c r="E85">
         <f t="shared" si="6"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F85">
         <f t="shared" si="7"/>
-        <v>49.5</v>
+        <v>49.545000000000002</v>
       </c>
       <c r="K85" t="s">
         <v>120</v>
@@ -3668,11 +3691,11 @@
       </c>
       <c r="E86">
         <f t="shared" si="6"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F86">
         <f t="shared" si="7"/>
-        <v>111.46666666666667</v>
+        <v>111.56800000000001</v>
       </c>
       <c r="K86" t="s">
         <v>121</v>
@@ -3698,11 +3721,11 @@
       </c>
       <c r="E87">
         <f t="shared" si="6"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F87">
         <f t="shared" si="7"/>
-        <v>59.289999999999992</v>
+        <v>59.343899999999991</v>
       </c>
       <c r="K87" t="s">
         <v>122</v>
@@ -3728,11 +3751,11 @@
       </c>
       <c r="E88">
         <f t="shared" si="6"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F88">
         <f t="shared" si="7"/>
-        <v>120.11999999999999</v>
+        <v>120.22919999999999</v>
       </c>
       <c r="K88" t="s">
         <v>123</v>
@@ -3758,11 +3781,11 @@
       </c>
       <c r="E89">
         <f t="shared" si="6"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F89">
         <f t="shared" si="7"/>
-        <v>95.59</v>
+        <v>95.676900000000003</v>
       </c>
       <c r="K89" t="s">
         <v>124</v>
@@ -3788,11 +3811,11 @@
       </c>
       <c r="E90">
         <f t="shared" si="6"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F90">
         <f t="shared" si="7"/>
-        <v>64.533333333333331</v>
+        <v>64.591999999999999</v>
       </c>
       <c r="K90" t="s">
         <v>125</v>
@@ -3818,11 +3841,11 @@
       </c>
       <c r="E91">
         <f t="shared" si="6"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F91">
         <f t="shared" si="7"/>
-        <v>20.790000000000003</v>
+        <v>20.808900000000001</v>
       </c>
       <c r="K91" t="s">
         <v>126</v>
@@ -3848,11 +3871,11 @@
       </c>
       <c r="E92">
         <f t="shared" si="6"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F92">
         <f t="shared" si="7"/>
-        <v>93.206666666666649</v>
+        <v>93.291399999999996</v>
       </c>
       <c r="K92" t="s">
         <v>127</v>
@@ -3878,11 +3901,11 @@
       </c>
       <c r="E93">
         <f t="shared" si="6"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F93">
         <f t="shared" si="7"/>
-        <v>82.17</v>
+        <v>82.244699999999995</v>
       </c>
       <c r="K93" t="s">
         <v>128</v>
@@ -3908,11 +3931,11 @@
       </c>
       <c r="E94">
         <f t="shared" si="6"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="F94">
         <f t="shared" si="7"/>
-        <v>15.4</v>
+        <v>15.414</v>
       </c>
       <c r="K94" t="s">
         <v>129</v>
@@ -3960,8 +3983,8 @@
         <v>23</v>
       </c>
       <c r="H7">
-        <f>44/12</f>
-        <v>3.6666666666666665</v>
+        <f>[1]!common_cco2</f>
+        <v>3.67</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -4001,11 +4024,11 @@
       </c>
       <c r="D11">
         <f>$H$7</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="E11">
         <f>A11*C11*D11*-1</f>
-        <v>-641.66666666666663</v>
+        <v>-642.25</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -4017,11 +4040,11 @@
       </c>
       <c r="D12">
         <f>$H$7</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="E12">
         <f>A12*C12*D12*-1</f>
-        <v>-292.16000000000003</v>
+        <v>-292.42560000000003</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.2">
@@ -4033,11 +4056,11 @@
       </c>
       <c r="D21">
         <f>$H$7</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="E21">
         <f>B21*C21*D21*-1</f>
-        <v>-45.833333333333329</v>
+        <v>-45.875</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
@@ -4049,11 +4072,11 @@
       </c>
       <c r="D22">
         <f>$H$7</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="E22">
         <f>B22*C22*D22*-1</f>
-        <v>-1339.0666666666668</v>
+        <v>-1340.2840000000001</v>
       </c>
     </row>
   </sheetData>
